--- a/public/downloads/gaizen-asset-tracking-template.xlsx
+++ b/public/downloads/gaizen-asset-tracking-template.xlsx
@@ -1,37 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\ubuntu\home\ugawa\project\gaizen\public\downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD581A5-2087-47E1-B936-4F2BBCC8F36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="資産記録" sheetId="1" r:id="rId1"/>
     <sheet name="ダッシュボード" sheetId="2" r:id="rId2"/>
     <sheet name="使い方" sheetId="3" r:id="rId3"/>
+    <sheet name="記入例（架空）" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">資産記録!$A$1:$N$44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">資産記録!$1:$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>GAIZEN FINANCE</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -49,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
   <si>
     <t>月次資産記録</t>
   </si>
@@ -231,7 +226,7 @@
     <t>前月比（率）</t>
   </si>
   <si>
-    <t>年初比（金額）</t>
+    <t>1月末比（金額）</t>
   </si>
   <si>
     <t>入力件数</t>
@@ -252,7 +247,7 @@
     <t>直近の前月比</t>
   </si>
   <si>
-    <t>年初からの増減</t>
+    <t>1月末からの増減</t>
   </si>
   <si>
     <t>入力は月1回、同じタイミングで。短期の上下より、年単位で積み上がっているかを確認します。</t>
@@ -291,25 +286,37 @@
     <t>Googleドライブで［新規］→［ファイルのアップロード］からこのExcelファイルを選び、Googleスプレッドシートとして開きます。取り込み後は、ご自身のGoogleアカウント内で管理してください。配布元のGoogleアカウントや個人情報はこのファイルに含まれていません。</t>
   </si>
   <si>
-    <t>本テンプレートは家計と資産残高を把握するための記録用です。特定の金融商品への投資を推奨するものではなく、正確な運用利回りや税務上の損益を計算するものでもありません。</t>
+    <t>未記録の月は全欄を空欄にし、確認済みの残高ゼロには0を入力します。一部の口座だけ入力した月も集計されるため、全口座を確認してから比較してください。借入残高を差し引く純資産や、運用利回り・税務上の損益を計算する表ではありません。1月末比は1月末の残高との比較で、暦年の年間損益ではありません。</t>
   </si>
   <si>
     <t>GAIZEN FINANCE｜資産額を毎月記録する方法</t>
+  </si>
+  <si>
+    <t>記入例（架空の金額・単位：円）</t>
+  </si>
+  <si>
+    <t>筆者の実績ではありません。入力用シートやダッシュボードとは連動していない、計算の説明用シートです。</t>
+  </si>
+  <si>
+    <t>口座</t>
+  </si>
+  <si>
+    <t>2月の増加7万円は運用益とは限りません。仮に給与等の収入30万円、生活費等の支出24万円なら、差し引き入金は6万円。残る1万円も、入出金・記録漏れを照合して初めて運用損益等と判断できます。銀行から証券への振替は合計を増やしません。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="#,##0;[Red]\-#,##0;&quot;-&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.0%;[Red]\-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0;&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0%;[Red]-0.0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -317,14 +324,14 @@
       <b/>
       <sz val="20"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF64748B"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -332,7 +339,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -340,7 +347,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -348,14 +355,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF64748B"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF64748B"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -363,7 +370,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FF132238"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -371,14 +378,14 @@
       <b/>
       <sz val="13"/>
       <color rgb="FF087F5B"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF132238"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -394,13 +401,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="15">
@@ -572,25 +572,43 @@
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -599,43 +617,24 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -645,10 +644,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -658,30 +658,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ja-JP"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="110"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="10"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="10"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -699,15 +682,13 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -724,7 +705,6 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>資産記録!$C$4:$N$4</c:f>
@@ -773,16 +753,16 @@
             <c:numRef>
               <c:f>資産記録!$C$41:$N$41</c:f>
               <c:numCache>
-                <c:formatCode>#,##0;[Red]\-#,##0;"-"</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1102000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1252200</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1357000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -814,21 +794,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-38CE-4498-8162-A7B4BFC78A70}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:barChart>
@@ -837,7 +803,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -855,25 +820,20 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -892,11 +852,9 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="#,##0,&quot;千&quot;" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -912,8 +870,6 @@
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -934,18 +890,9 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ja-JP"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="110"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="10"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="10"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -963,15 +910,13 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -986,7 +931,6 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>資産記録!$C$4:$N$4</c:f>
@@ -1035,16 +979,16 @@
             <c:numRef>
               <c:f>資産記録!$C$14:$N$14</c:f>
               <c:numCache>
-                <c:formatCode>#,##0;[Red]\-#,##0;"-"</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1000000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1100000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1200000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1076,11 +1020,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EDF2-4056-BB49-AF4B9040B123}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1096,7 +1035,6 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>資産記録!$C$4:$N$4</c:f>
@@ -1145,16 +1083,16 @@
             <c:numRef>
               <c:f>資産記録!$C$19:$N$19</c:f>
               <c:numCache>
-                <c:formatCode>#,##0;[Red]\-#,##0;"-"</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>100000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>155000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1186,11 +1124,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EDF2-4056-BB49-AF4B9040B123}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1206,7 +1139,6 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>資産記録!$C$4:$N$4</c:f>
@@ -1255,7 +1187,7 @@
             <c:numRef>
               <c:f>資産記録!$C$21:$N$21</c:f>
               <c:numCache>
-                <c:formatCode>#,##0;[Red]\-#,##0;"-"</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1296,11 +1228,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-EDF2-4056-BB49-AF4B9040B123}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1316,7 +1243,6 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>資産記録!$C$4:$N$4</c:f>
@@ -1365,7 +1291,7 @@
             <c:numRef>
               <c:f>資産記録!$C$23:$N$23</c:f>
               <c:numCache>
-                <c:formatCode>#,##0;[Red]\-#,##0;"-"</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1406,11 +1332,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-EDF2-4056-BB49-AF4B9040B123}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -1426,7 +1347,6 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>資産記録!$C$4:$N$4</c:f>
@@ -1475,16 +1395,16 @@
             <c:numRef>
               <c:f>資産記録!$C$32:$N$32</c:f>
               <c:numCache>
-                <c:formatCode>#,##0;[Red]\-#,##0;"-"</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>2000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2200</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1516,11 +1436,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-EDF2-4056-BB49-AF4B9040B123}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="5"/>
@@ -1536,7 +1451,6 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>資産記録!$C$4:$N$4</c:f>
@@ -1585,7 +1499,7 @@
             <c:numRef>
               <c:f>資産記録!$C$36:$N$36</c:f>
               <c:numCache>
-                <c:formatCode>#,##0;[Red]\-#,##0;"-"</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1626,11 +1540,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-EDF2-4056-BB49-AF4B9040B123}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="6"/>
@@ -1646,7 +1555,6 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>資産記録!$C$4:$N$4</c:f>
@@ -1695,7 +1603,7 @@
             <c:numRef>
               <c:f>資産記録!$C$38:$N$38</c:f>
               <c:numCache>
-                <c:formatCode>#,##0;[Red]\-#,##0;"-"</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1736,11 +1644,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-EDF2-4056-BB49-AF4B9040B123}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="7"/>
@@ -1756,7 +1659,6 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>資産記録!$C$4:$N$4</c:f>
@@ -1805,7 +1707,7 @@
             <c:numRef>
               <c:f>資産記録!$C$40:$N$40</c:f>
               <c:numCache>
-                <c:formatCode>#,##0;[Red]\-#,##0;"-"</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1846,21 +1748,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-EDF2-4056-BB49-AF4B9040B123}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
         <c:overlap val="100"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
@@ -1870,7 +1758,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1888,25 +1775,20 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -1925,11 +1807,9 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="#,##0,&quot;千&quot;" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -1946,11 +1826,9 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1962,6 +1840,139 @@
       </a:solidFill>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>架空の記入例：総資産の推移</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>総資産（架空）</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00A86B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'記入例（架空）'!$B$5:$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2026年1月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2026年2月</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026年3月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'記入例（架空）'!$B$10:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1900000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1970000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1980000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50030001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50030002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>円</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1987,13 +1998,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2023,13 +2028,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2047,10 +2046,45 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2088,7 +2122,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2122,7 +2156,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2157,10 +2190,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2333,1359 +2365,1415 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF00A86B"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N45"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.75" customWidth="1"/>
-    <col min="2" max="2" width="22.75" customWidth="1"/>
-    <col min="3" max="14" width="14.75" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="14" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:14" ht="34" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-    </row>
-    <row r="4" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="4" spans="1:14" ht="28" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:14">
+      <c r="A5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1100000</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1200000</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
-      <c r="B6" s="2" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
-      <c r="B7" s="2" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
-      <c r="B8" s="2" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A9" s="16"/>
-      <c r="B9" s="2" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
-      <c r="B10" s="2" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A11" s="16"/>
-      <c r="B11" s="2" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A12" s="16"/>
-      <c r="B12" s="2" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A13" s="16"/>
-      <c r="B13" s="2" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="5">
-        <f t="shared" ref="C14:N14" si="0">SUM(C5:C13)</f>
-        <v>1000000</v>
-      </c>
-      <c r="D14" s="5">
-        <f t="shared" si="0"/>
-        <v>1100000</v>
-      </c>
-      <c r="E14" s="5">
-        <f t="shared" si="0"/>
-        <v>1200000</v>
-      </c>
-      <c r="F14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A15" s="17" t="s">
+      <c r="C14" s="8">
+        <f>IF(COUNT(C5:C13)=0,"",SUM(C5:C13))</f>
+        <v/>
+      </c>
+      <c r="D14" s="8">
+        <f>IF(COUNT(D5:D13)=0,"",SUM(D5:D13))</f>
+        <v/>
+      </c>
+      <c r="E14" s="8">
+        <f>IF(COUNT(E5:E13)=0,"",SUM(E5:E13))</f>
+        <v/>
+      </c>
+      <c r="F14" s="8">
+        <f>IF(COUNT(F5:F13)=0,"",SUM(F5:F13))</f>
+        <v/>
+      </c>
+      <c r="G14" s="8">
+        <f>IF(COUNT(G5:G13)=0,"",SUM(G5:G13))</f>
+        <v/>
+      </c>
+      <c r="H14" s="8">
+        <f>IF(COUNT(H5:H13)=0,"",SUM(H5:H13))</f>
+        <v/>
+      </c>
+      <c r="I14" s="8">
+        <f>IF(COUNT(I5:I13)=0,"",SUM(I5:I13))</f>
+        <v/>
+      </c>
+      <c r="J14" s="8">
+        <f>IF(COUNT(J5:J13)=0,"",SUM(J5:J13))</f>
+        <v/>
+      </c>
+      <c r="K14" s="8">
+        <f>IF(COUNT(K5:K13)=0,"",SUM(K5:K13))</f>
+        <v/>
+      </c>
+      <c r="L14" s="8">
+        <f>IF(COUNT(L5:L13)=0,"",SUM(L5:L13))</f>
+        <v/>
+      </c>
+      <c r="M14" s="8">
+        <f>IF(COUNT(M5:M13)=0,"",SUM(M5:M13))</f>
+        <v/>
+      </c>
+      <c r="N14" s="8">
+        <f>IF(COUNT(N5:N13)=0,"",SUM(N5:N13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="3">
-        <v>100000</v>
-      </c>
-      <c r="D15" s="3">
-        <v>150000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>155000</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A16" s="17"/>
-      <c r="B16" s="2" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="9"/>
+      <c r="B16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A17" s="17"/>
-      <c r="B17" s="2" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="9"/>
+      <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A18" s="17"/>
-      <c r="B18" s="2" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="9"/>
+      <c r="B18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="5">
-        <f t="shared" ref="C19:N19" si="1">SUM(C15:C18)</f>
-        <v>100000</v>
-      </c>
-      <c r="D19" s="5">
-        <f t="shared" si="1"/>
-        <v>150000</v>
-      </c>
-      <c r="E19" s="5">
-        <f t="shared" si="1"/>
-        <v>155000</v>
-      </c>
-      <c r="F19" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A20" s="6" t="s">
+      <c r="C19" s="8">
+        <f>IF(COUNT(C15:C18)=0,"",SUM(C15:C18))</f>
+        <v/>
+      </c>
+      <c r="D19" s="8">
+        <f>IF(COUNT(D15:D18)=0,"",SUM(D15:D18))</f>
+        <v/>
+      </c>
+      <c r="E19" s="8">
+        <f>IF(COUNT(E15:E18)=0,"",SUM(E15:E18))</f>
+        <v/>
+      </c>
+      <c r="F19" s="8">
+        <f>IF(COUNT(F15:F18)=0,"",SUM(F15:F18))</f>
+        <v/>
+      </c>
+      <c r="G19" s="8">
+        <f>IF(COUNT(G15:G18)=0,"",SUM(G15:G18))</f>
+        <v/>
+      </c>
+      <c r="H19" s="8">
+        <f>IF(COUNT(H15:H18)=0,"",SUM(H15:H18))</f>
+        <v/>
+      </c>
+      <c r="I19" s="8">
+        <f>IF(COUNT(I15:I18)=0,"",SUM(I15:I18))</f>
+        <v/>
+      </c>
+      <c r="J19" s="8">
+        <f>IF(COUNT(J15:J18)=0,"",SUM(J15:J18))</f>
+        <v/>
+      </c>
+      <c r="K19" s="8">
+        <f>IF(COUNT(K15:K18)=0,"",SUM(K15:K18))</f>
+        <v/>
+      </c>
+      <c r="L19" s="8">
+        <f>IF(COUNT(L15:L18)=0,"",SUM(L15:L18))</f>
+        <v/>
+      </c>
+      <c r="M19" s="8">
+        <f>IF(COUNT(M15:M18)=0,"",SUM(M15:M18))</f>
+        <v/>
+      </c>
+      <c r="N19" s="8">
+        <f>IF(COUNT(N15:N18)=0,"",SUM(N15:N18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4" t="s">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="5">
-        <f t="shared" ref="C21:N21" si="2">SUM(C20:C20)</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A22" s="7" t="s">
+      <c r="C21" s="8">
+        <f>IF(COUNT(C20:C20)=0,"",SUM(C20:C20))</f>
+        <v/>
+      </c>
+      <c r="D21" s="8">
+        <f>IF(COUNT(D20:D20)=0,"",SUM(D20:D20))</f>
+        <v/>
+      </c>
+      <c r="E21" s="8">
+        <f>IF(COUNT(E20:E20)=0,"",SUM(E20:E20))</f>
+        <v/>
+      </c>
+      <c r="F21" s="8">
+        <f>IF(COUNT(F20:F20)=0,"",SUM(F20:F20))</f>
+        <v/>
+      </c>
+      <c r="G21" s="8">
+        <f>IF(COUNT(G20:G20)=0,"",SUM(G20:G20))</f>
+        <v/>
+      </c>
+      <c r="H21" s="8">
+        <f>IF(COUNT(H20:H20)=0,"",SUM(H20:H20))</f>
+        <v/>
+      </c>
+      <c r="I21" s="8">
+        <f>IF(COUNT(I20:I20)=0,"",SUM(I20:I20))</f>
+        <v/>
+      </c>
+      <c r="J21" s="8">
+        <f>IF(COUNT(J20:J20)=0,"",SUM(J20:J20))</f>
+        <v/>
+      </c>
+      <c r="K21" s="8">
+        <f>IF(COUNT(K20:K20)=0,"",SUM(K20:K20))</f>
+        <v/>
+      </c>
+      <c r="L21" s="8">
+        <f>IF(COUNT(L20:L20)=0,"",SUM(L20:L20))</f>
+        <v/>
+      </c>
+      <c r="M21" s="8">
+        <f>IF(COUNT(M20:M20)=0,"",SUM(M20:M20))</f>
+        <v/>
+      </c>
+      <c r="N21" s="8">
+        <f>IF(COUNT(N20:N20)=0,"",SUM(N20:N20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4" t="s">
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="5">
-        <f t="shared" ref="C23:N23" si="3">SUM(C22:C22)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A24" s="18" t="s">
+      <c r="C23" s="8">
+        <f>IF(COUNT(C22:C22)=0,"",SUM(C22:C22))</f>
+        <v/>
+      </c>
+      <c r="D23" s="8">
+        <f>IF(COUNT(D22:D22)=0,"",SUM(D22:D22))</f>
+        <v/>
+      </c>
+      <c r="E23" s="8">
+        <f>IF(COUNT(E22:E22)=0,"",SUM(E22:E22))</f>
+        <v/>
+      </c>
+      <c r="F23" s="8">
+        <f>IF(COUNT(F22:F22)=0,"",SUM(F22:F22))</f>
+        <v/>
+      </c>
+      <c r="G23" s="8">
+        <f>IF(COUNT(G22:G22)=0,"",SUM(G22:G22))</f>
+        <v/>
+      </c>
+      <c r="H23" s="8">
+        <f>IF(COUNT(H22:H22)=0,"",SUM(H22:H22))</f>
+        <v/>
+      </c>
+      <c r="I23" s="8">
+        <f>IF(COUNT(I22:I22)=0,"",SUM(I22:I22))</f>
+        <v/>
+      </c>
+      <c r="J23" s="8">
+        <f>IF(COUNT(J22:J22)=0,"",SUM(J22:J22))</f>
+        <v/>
+      </c>
+      <c r="K23" s="8">
+        <f>IF(COUNT(K22:K22)=0,"",SUM(K22:K22))</f>
+        <v/>
+      </c>
+      <c r="L23" s="8">
+        <f>IF(COUNT(L22:L22)=0,"",SUM(L22:L22))</f>
+        <v/>
+      </c>
+      <c r="M23" s="8">
+        <f>IF(COUNT(M22:M22)=0,"",SUM(M22:M22))</f>
+        <v/>
+      </c>
+      <c r="N23" s="8">
+        <f>IF(COUNT(N22:N22)=0,"",SUM(N22:N22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A25" s="18"/>
-      <c r="B25" s="2" t="s">
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="12"/>
+      <c r="B25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A26" s="18"/>
-      <c r="B26" s="2" t="s">
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="12"/>
+      <c r="B26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A27" s="18"/>
-      <c r="B27" s="2" t="s">
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="12"/>
+      <c r="B27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="D27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A28" s="18"/>
-      <c r="B28" s="2" t="s">
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="12"/>
+      <c r="B28" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A29" s="18"/>
-      <c r="B29" s="2" t="s">
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="12"/>
+      <c r="B29" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A30" s="18"/>
-      <c r="B30" s="2" t="s">
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="12"/>
+      <c r="B30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A31" s="18"/>
-      <c r="B31" s="2" t="s">
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="12"/>
+      <c r="B31" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4" t="s">
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="5">
-        <f t="shared" ref="C32:N32" si="4">SUM(C24:C31)</f>
-        <v>2000</v>
-      </c>
-      <c r="D32" s="5">
-        <f t="shared" si="4"/>
-        <v>2200</v>
-      </c>
-      <c r="E32" s="5">
-        <f t="shared" si="4"/>
-        <v>2000</v>
-      </c>
-      <c r="F32" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N32" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A33" s="19" t="s">
+      <c r="C32" s="8">
+        <f>IF(COUNT(C24:C31)=0,"",SUM(C24:C31))</f>
+        <v/>
+      </c>
+      <c r="D32" s="8">
+        <f>IF(COUNT(D24:D31)=0,"",SUM(D24:D31))</f>
+        <v/>
+      </c>
+      <c r="E32" s="8">
+        <f>IF(COUNT(E24:E31)=0,"",SUM(E24:E31))</f>
+        <v/>
+      </c>
+      <c r="F32" s="8">
+        <f>IF(COUNT(F24:F31)=0,"",SUM(F24:F31))</f>
+        <v/>
+      </c>
+      <c r="G32" s="8">
+        <f>IF(COUNT(G24:G31)=0,"",SUM(G24:G31))</f>
+        <v/>
+      </c>
+      <c r="H32" s="8">
+        <f>IF(COUNT(H24:H31)=0,"",SUM(H24:H31))</f>
+        <v/>
+      </c>
+      <c r="I32" s="8">
+        <f>IF(COUNT(I24:I31)=0,"",SUM(I24:I31))</f>
+        <v/>
+      </c>
+      <c r="J32" s="8">
+        <f>IF(COUNT(J24:J31)=0,"",SUM(J24:J31))</f>
+        <v/>
+      </c>
+      <c r="K32" s="8">
+        <f>IF(COUNT(K24:K31)=0,"",SUM(K24:K31))</f>
+        <v/>
+      </c>
+      <c r="L32" s="8">
+        <f>IF(COUNT(L24:L31)=0,"",SUM(L24:L31))</f>
+        <v/>
+      </c>
+      <c r="M32" s="8">
+        <f>IF(COUNT(M24:M31)=0,"",SUM(M24:M31))</f>
+        <v/>
+      </c>
+      <c r="N32" s="8">
+        <f>IF(COUNT(N24:N31)=0,"",SUM(N24:N31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A34" s="19"/>
-      <c r="B34" s="2" t="s">
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="13"/>
+      <c r="B34" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A35" s="19"/>
-      <c r="B35" s="2" t="s">
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="13"/>
+      <c r="B35" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4" t="s">
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="5">
-        <f t="shared" ref="C36:N36" si="5">SUM(C33:C35)</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N36" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A37" s="8" t="s">
+      <c r="C36" s="8">
+        <f>IF(COUNT(C33:C35)=0,"",SUM(C33:C35))</f>
+        <v/>
+      </c>
+      <c r="D36" s="8">
+        <f>IF(COUNT(D33:D35)=0,"",SUM(D33:D35))</f>
+        <v/>
+      </c>
+      <c r="E36" s="8">
+        <f>IF(COUNT(E33:E35)=0,"",SUM(E33:E35))</f>
+        <v/>
+      </c>
+      <c r="F36" s="8">
+        <f>IF(COUNT(F33:F35)=0,"",SUM(F33:F35))</f>
+        <v/>
+      </c>
+      <c r="G36" s="8">
+        <f>IF(COUNT(G33:G35)=0,"",SUM(G33:G35))</f>
+        <v/>
+      </c>
+      <c r="H36" s="8">
+        <f>IF(COUNT(H33:H35)=0,"",SUM(H33:H35))</f>
+        <v/>
+      </c>
+      <c r="I36" s="8">
+        <f>IF(COUNT(I33:I35)=0,"",SUM(I33:I35))</f>
+        <v/>
+      </c>
+      <c r="J36" s="8">
+        <f>IF(COUNT(J33:J35)=0,"",SUM(J33:J35))</f>
+        <v/>
+      </c>
+      <c r="K36" s="8">
+        <f>IF(COUNT(K33:K35)=0,"",SUM(K33:K35))</f>
+        <v/>
+      </c>
+      <c r="L36" s="8">
+        <f>IF(COUNT(L33:L35)=0,"",SUM(L33:L35))</f>
+        <v/>
+      </c>
+      <c r="M36" s="8">
+        <f>IF(COUNT(M33:M35)=0,"",SUM(M33:M35))</f>
+        <v/>
+      </c>
+      <c r="N36" s="8">
+        <f>IF(COUNT(N33:N35)=0,"",SUM(N33:N35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4" t="s">
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="5">
-        <f t="shared" ref="C38:N38" si="6">SUM(C37:C37)</f>
-        <v>0</v>
-      </c>
-      <c r="D38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A39" s="9" t="s">
+      <c r="C38" s="8">
+        <f>IF(COUNT(C37:C37)=0,"",SUM(C37:C37))</f>
+        <v/>
+      </c>
+      <c r="D38" s="8">
+        <f>IF(COUNT(D37:D37)=0,"",SUM(D37:D37))</f>
+        <v/>
+      </c>
+      <c r="E38" s="8">
+        <f>IF(COUNT(E37:E37)=0,"",SUM(E37:E37))</f>
+        <v/>
+      </c>
+      <c r="F38" s="8">
+        <f>IF(COUNT(F37:F37)=0,"",SUM(F37:F37))</f>
+        <v/>
+      </c>
+      <c r="G38" s="8">
+        <f>IF(COUNT(G37:G37)=0,"",SUM(G37:G37))</f>
+        <v/>
+      </c>
+      <c r="H38" s="8">
+        <f>IF(COUNT(H37:H37)=0,"",SUM(H37:H37))</f>
+        <v/>
+      </c>
+      <c r="I38" s="8">
+        <f>IF(COUNT(I37:I37)=0,"",SUM(I37:I37))</f>
+        <v/>
+      </c>
+      <c r="J38" s="8">
+        <f>IF(COUNT(J37:J37)=0,"",SUM(J37:J37))</f>
+        <v/>
+      </c>
+      <c r="K38" s="8">
+        <f>IF(COUNT(K37:K37)=0,"",SUM(K37:K37))</f>
+        <v/>
+      </c>
+      <c r="L38" s="8">
+        <f>IF(COUNT(L37:L37)=0,"",SUM(L37:L37))</f>
+        <v/>
+      </c>
+      <c r="M38" s="8">
+        <f>IF(COUNT(M37:M37)=0,"",SUM(M37:M37))</f>
+        <v/>
+      </c>
+      <c r="N38" s="8">
+        <f>IF(COUNT(N37:N37)=0,"",SUM(N37:N37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4" t="s">
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="5">
-        <f t="shared" ref="C40:N40" si="7">SUM(C39:C39)</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N40" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="20" t="s">
+      <c r="C40" s="8">
+        <f>IF(COUNT(C39:C39)=0,"",SUM(C39:C39))</f>
+        <v/>
+      </c>
+      <c r="D40" s="8">
+        <f>IF(COUNT(D39:D39)=0,"",SUM(D39:D39))</f>
+        <v/>
+      </c>
+      <c r="E40" s="8">
+        <f>IF(COUNT(E39:E39)=0,"",SUM(E39:E39))</f>
+        <v/>
+      </c>
+      <c r="F40" s="8">
+        <f>IF(COUNT(F39:F39)=0,"",SUM(F39:F39))</f>
+        <v/>
+      </c>
+      <c r="G40" s="8">
+        <f>IF(COUNT(G39:G39)=0,"",SUM(G39:G39))</f>
+        <v/>
+      </c>
+      <c r="H40" s="8">
+        <f>IF(COUNT(H39:H39)=0,"",SUM(H39:H39))</f>
+        <v/>
+      </c>
+      <c r="I40" s="8">
+        <f>IF(COUNT(I39:I39)=0,"",SUM(I39:I39))</f>
+        <v/>
+      </c>
+      <c r="J40" s="8">
+        <f>IF(COUNT(J39:J39)=0,"",SUM(J39:J39))</f>
+        <v/>
+      </c>
+      <c r="K40" s="8">
+        <f>IF(COUNT(K39:K39)=0,"",SUM(K39:K39))</f>
+        <v/>
+      </c>
+      <c r="L40" s="8">
+        <f>IF(COUNT(L39:L39)=0,"",SUM(L39:L39))</f>
+        <v/>
+      </c>
+      <c r="M40" s="8">
+        <f>IF(COUNT(M39:M39)=0,"",SUM(M39:M39))</f>
+        <v/>
+      </c>
+      <c r="N40" s="8">
+        <f>IF(COUNT(N39:N39)=0,"",SUM(N39:N39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="24" customHeight="1">
+      <c r="A41" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B41" s="20"/>
-      <c r="C41" s="10">
-        <f t="shared" ref="C41:N41" si="8">C14+C19+C21+C23+C32+C36+C38+C40</f>
-        <v>1102000</v>
-      </c>
-      <c r="D41" s="10">
-        <f t="shared" si="8"/>
-        <v>1252200</v>
-      </c>
-      <c r="E41" s="10">
-        <f t="shared" si="8"/>
-        <v>1357000</v>
-      </c>
-      <c r="F41" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G41" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L41" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N41" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A42" s="21" t="s">
+      <c r="B41" s="16"/>
+      <c r="C41" s="17">
+        <f>IF(COUNT(C5,C6,C7,C8,C9,C10,C11,C12,C13,C15,C16,C17,C18,C20,C22,C24,C25,C26,C27,C28,C29,C30,C31,C33,C34,C35,C37,C39)=0,"",SUM(C14,C19,C21,C23,C32,C36,C38,C40))</f>
+        <v/>
+      </c>
+      <c r="D41" s="17">
+        <f>IF(COUNT(D5,D6,D7,D8,D9,D10,D11,D12,D13,D15,D16,D17,D18,D20,D22,D24,D25,D26,D27,D28,D29,D30,D31,D33,D34,D35,D37,D39)=0,"",SUM(D14,D19,D21,D23,D32,D36,D38,D40))</f>
+        <v/>
+      </c>
+      <c r="E41" s="17">
+        <f>IF(COUNT(E5,E6,E7,E8,E9,E10,E11,E12,E13,E15,E16,E17,E18,E20,E22,E24,E25,E26,E27,E28,E29,E30,E31,E33,E34,E35,E37,E39)=0,"",SUM(E14,E19,E21,E23,E32,E36,E38,E40))</f>
+        <v/>
+      </c>
+      <c r="F41" s="17">
+        <f>IF(COUNT(F5,F6,F7,F8,F9,F10,F11,F12,F13,F15,F16,F17,F18,F20,F22,F24,F25,F26,F27,F28,F29,F30,F31,F33,F34,F35,F37,F39)=0,"",SUM(F14,F19,F21,F23,F32,F36,F38,F40))</f>
+        <v/>
+      </c>
+      <c r="G41" s="17">
+        <f>IF(COUNT(G5,G6,G7,G8,G9,G10,G11,G12,G13,G15,G16,G17,G18,G20,G22,G24,G25,G26,G27,G28,G29,G30,G31,G33,G34,G35,G37,G39)=0,"",SUM(G14,G19,G21,G23,G32,G36,G38,G40))</f>
+        <v/>
+      </c>
+      <c r="H41" s="17">
+        <f>IF(COUNT(H5,H6,H7,H8,H9,H10,H11,H12,H13,H15,H16,H17,H18,H20,H22,H24,H25,H26,H27,H28,H29,H30,H31,H33,H34,H35,H37,H39)=0,"",SUM(H14,H19,H21,H23,H32,H36,H38,H40))</f>
+        <v/>
+      </c>
+      <c r="I41" s="17">
+        <f>IF(COUNT(I5,I6,I7,I8,I9,I10,I11,I12,I13,I15,I16,I17,I18,I20,I22,I24,I25,I26,I27,I28,I29,I30,I31,I33,I34,I35,I37,I39)=0,"",SUM(I14,I19,I21,I23,I32,I36,I38,I40))</f>
+        <v/>
+      </c>
+      <c r="J41" s="17">
+        <f>IF(COUNT(J5,J6,J7,J8,J9,J10,J11,J12,J13,J15,J16,J17,J18,J20,J22,J24,J25,J26,J27,J28,J29,J30,J31,J33,J34,J35,J37,J39)=0,"",SUM(J14,J19,J21,J23,J32,J36,J38,J40))</f>
+        <v/>
+      </c>
+      <c r="K41" s="17">
+        <f>IF(COUNT(K5,K6,K7,K8,K9,K10,K11,K12,K13,K15,K16,K17,K18,K20,K22,K24,K25,K26,K27,K28,K29,K30,K31,K33,K34,K35,K37,K39)=0,"",SUM(K14,K19,K21,K23,K32,K36,K38,K40))</f>
+        <v/>
+      </c>
+      <c r="L41" s="17">
+        <f>IF(COUNT(L5,L6,L7,L8,L9,L10,L11,L12,L13,L15,L16,L17,L18,L20,L22,L24,L25,L26,L27,L28,L29,L30,L31,L33,L34,L35,L37,L39)=0,"",SUM(L14,L19,L21,L23,L32,L36,L38,L40))</f>
+        <v/>
+      </c>
+      <c r="M41" s="17">
+        <f>IF(COUNT(M5,M6,M7,M8,M9,M10,M11,M12,M13,M15,M16,M17,M18,M20,M22,M24,M25,M26,M27,M28,M29,M30,M31,M33,M34,M35,M37,M39)=0,"",SUM(M14,M19,M21,M23,M32,M36,M38,M40))</f>
+        <v/>
+      </c>
+      <c r="N41" s="17">
+        <f>IF(COUNT(N5,N6,N7,N8,N9,N10,N11,N12,N13,N15,N16,N17,N18,N20,N22,N24,N25,N26,N27,N28,N29,N30,N31,N33,N34,N35,N37,N39)=0,"",SUM(N14,N19,N21,N23,N32,N36,N38,N40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11">
-        <f t="shared" ref="D42:N42" si="9">D41-C41</f>
-        <v>150200</v>
-      </c>
-      <c r="E42" s="11">
-        <f t="shared" si="9"/>
-        <v>104800</v>
-      </c>
-      <c r="F42" s="11">
-        <f t="shared" si="9"/>
-        <v>-1357000</v>
-      </c>
-      <c r="G42" s="11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L42" s="11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N42" s="11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A43" s="21" t="s">
+      <c r="B42" s="18"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19">
+        <f>IF(COUNT(D41,C41)&lt;2,"",D41-C41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="19">
+        <f>IF(COUNT(E41,D41)&lt;2,"",E41-D41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="19">
+        <f>IF(COUNT(F41,E41)&lt;2,"",F41-E41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="19">
+        <f>IF(COUNT(G41,F41)&lt;2,"",G41-F41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="19">
+        <f>IF(COUNT(H41,G41)&lt;2,"",H41-G41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="19">
+        <f>IF(COUNT(I41,H41)&lt;2,"",I41-H41)</f>
+        <v/>
+      </c>
+      <c r="J42" s="19">
+        <f>IF(COUNT(J41,I41)&lt;2,"",J41-I41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="19">
+        <f>IF(COUNT(K41,J41)&lt;2,"",K41-J41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="19">
+        <f>IF(COUNT(L41,K41)&lt;2,"",L41-K41)</f>
+        <v/>
+      </c>
+      <c r="M42" s="19">
+        <f>IF(COUNT(M41,L41)&lt;2,"",M41-L41)</f>
+        <v/>
+      </c>
+      <c r="N42" s="19">
+        <f>IF(COUNT(N41,M41)&lt;2,"",N41-M41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12">
-        <f t="shared" ref="D43:N43" si="10">IFERROR(D41/C41-1,"")</f>
-        <v>0.13629764065335759</v>
-      </c>
-      <c r="E43" s="12">
-        <f t="shared" si="10"/>
-        <v>8.3692700846510037E-2</v>
-      </c>
-      <c r="F43" s="12">
-        <f t="shared" si="10"/>
-        <v>-1</v>
-      </c>
-      <c r="G43" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H43" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="I43" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J43" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K43" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="L43" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M43" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="N43" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A44" s="21" t="s">
+      <c r="B43" s="18"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20">
+        <f>IF(COUNT(D41,C41)&lt;2,"",IFERROR(D41/C41-1,""))</f>
+        <v/>
+      </c>
+      <c r="E43" s="20">
+        <f>IF(COUNT(E41,D41)&lt;2,"",IFERROR(E41/D41-1,""))</f>
+        <v/>
+      </c>
+      <c r="F43" s="20">
+        <f>IF(COUNT(F41,E41)&lt;2,"",IFERROR(F41/E41-1,""))</f>
+        <v/>
+      </c>
+      <c r="G43" s="20">
+        <f>IF(COUNT(G41,F41)&lt;2,"",IFERROR(G41/F41-1,""))</f>
+        <v/>
+      </c>
+      <c r="H43" s="20">
+        <f>IF(COUNT(H41,G41)&lt;2,"",IFERROR(H41/G41-1,""))</f>
+        <v/>
+      </c>
+      <c r="I43" s="20">
+        <f>IF(COUNT(I41,H41)&lt;2,"",IFERROR(I41/H41-1,""))</f>
+        <v/>
+      </c>
+      <c r="J43" s="20">
+        <f>IF(COUNT(J41,I41)&lt;2,"",IFERROR(J41/I41-1,""))</f>
+        <v/>
+      </c>
+      <c r="K43" s="20">
+        <f>IF(COUNT(K41,J41)&lt;2,"",IFERROR(K41/J41-1,""))</f>
+        <v/>
+      </c>
+      <c r="L43" s="20">
+        <f>IF(COUNT(L41,K41)&lt;2,"",IFERROR(L41/K41-1,""))</f>
+        <v/>
+      </c>
+      <c r="M43" s="20">
+        <f>IF(COUNT(M41,L41)&lt;2,"",IFERROR(M41/L41-1,""))</f>
+        <v/>
+      </c>
+      <c r="N43" s="20">
+        <f>IF(COUNT(N41,M41)&lt;2,"",IFERROR(N41/M41-1,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="11">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="D44" s="11">
-        <f t="shared" ref="D44:N44" si="11">D41-$C$41</f>
-        <v>150200</v>
-      </c>
-      <c r="E44" s="11">
-        <f t="shared" si="11"/>
-        <v>255000</v>
-      </c>
-      <c r="F44" s="11">
-        <f t="shared" si="11"/>
-        <v>-1102000</v>
-      </c>
-      <c r="G44" s="11">
-        <f t="shared" si="11"/>
-        <v>-1102000</v>
-      </c>
-      <c r="H44" s="11">
-        <f t="shared" si="11"/>
-        <v>-1102000</v>
-      </c>
-      <c r="I44" s="11">
-        <f t="shared" si="11"/>
-        <v>-1102000</v>
-      </c>
-      <c r="J44" s="11">
-        <f t="shared" si="11"/>
-        <v>-1102000</v>
-      </c>
-      <c r="K44" s="11">
-        <f t="shared" si="11"/>
-        <v>-1102000</v>
-      </c>
-      <c r="L44" s="11">
-        <f t="shared" si="11"/>
-        <v>-1102000</v>
-      </c>
-      <c r="M44" s="11">
-        <f t="shared" si="11"/>
-        <v>-1102000</v>
-      </c>
-      <c r="N44" s="11">
-        <f t="shared" si="11"/>
-        <v>-1102000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="18"/>
+      <c r="C44" s="19">
+        <f>IF(ISNUMBER(C41),0,"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="19">
+        <f>IF(COUNT(D41,$C$41)&lt;2,"",D41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="E44" s="19">
+        <f>IF(COUNT(E41,$C$41)&lt;2,"",E41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="F44" s="19">
+        <f>IF(COUNT(F41,$C$41)&lt;2,"",F41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="G44" s="19">
+        <f>IF(COUNT(G41,$C$41)&lt;2,"",G41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="H44" s="19">
+        <f>IF(COUNT(H41,$C$41)&lt;2,"",H41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="I44" s="19">
+        <f>IF(COUNT(I41,$C$41)&lt;2,"",I41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="J44" s="19">
+        <f>IF(COUNT(J41,$C$41)&lt;2,"",J41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="K44" s="19">
+        <f>IF(COUNT(K41,$C$41)&lt;2,"",K41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="L44" s="19">
+        <f>IF(COUNT(L41,$C$41)&lt;2,"",L41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="M44" s="19">
+        <f>IF(COUNT(M41,$C$41)&lt;2,"",M41-$C$41)</f>
+        <v/>
+      </c>
+      <c r="N44" s="19">
+        <f>IF(COUNT(N41,$C$41)&lt;2,"",N41-$C$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:14" hidden="1">
       <c r="B45" t="s">
         <v>61</v>
       </c>
       <c r="C45">
-        <f t="shared" ref="C45:N45" si="12">COUNT(C5,C6,C7,C8,C9,C10,C11,C12,C13,C15,C16,C17,C18,C20,C22,C24,C25,C26,C27,C28,C29,C30,C31,C33,C34,C35,C37,C39)</f>
-        <v>4</v>
+        <f>COUNT(C5,C6,C7,C8,C9,C10,C11,C12,C13,C15,C16,C17,C18,C20,C22,C24,C25,C26,C27,C28,C29,C30,C31,C33,C34,C35,C37,C39)</f>
+        <v>0</v>
       </c>
       <c r="D45">
-        <f t="shared" si="12"/>
-        <v>4</v>
+        <f>COUNT(D5,D6,D7,D8,D9,D10,D11,D12,D13,D15,D16,D17,D18,D20,D22,D24,D25,D26,D27,D28,D29,D30,D31,D33,D34,D35,D37,D39)</f>
+        <v>0</v>
       </c>
       <c r="E45">
-        <f t="shared" si="12"/>
-        <v>4</v>
+        <f>COUNT(E5,E6,E7,E8,E9,E10,E11,E12,E13,E15,E16,E17,E18,E20,E22,E24,E25,E26,E27,E28,E29,E30,E31,E33,E34,E35,E37,E39)</f>
+        <v>0</v>
       </c>
       <c r="F45">
-        <f t="shared" si="12"/>
+        <f>COUNT(F5,F6,F7,F8,F9,F10,F11,F12,F13,F15,F16,F17,F18,F20,F22,F24,F25,F26,F27,F28,F29,F30,F31,F33,F34,F35,F37,F39)</f>
         <v>0</v>
       </c>
       <c r="G45">
-        <f t="shared" si="12"/>
+        <f>COUNT(G5,G6,G7,G8,G9,G10,G11,G12,G13,G15,G16,G17,G18,G20,G22,G24,G25,G26,G27,G28,G29,G30,G31,G33,G34,G35,G37,G39)</f>
         <v>0</v>
       </c>
       <c r="H45">
-        <f t="shared" si="12"/>
+        <f>COUNT(H5,H6,H7,H8,H9,H10,H11,H12,H13,H15,H16,H17,H18,H20,H22,H24,H25,H26,H27,H28,H29,H30,H31,H33,H34,H35,H37,H39)</f>
         <v>0</v>
       </c>
       <c r="I45">
-        <f t="shared" si="12"/>
+        <f>COUNT(I5,I6,I7,I8,I9,I10,I11,I12,I13,I15,I16,I17,I18,I20,I22,I24,I25,I26,I27,I28,I29,I30,I31,I33,I34,I35,I37,I39)</f>
         <v>0</v>
       </c>
       <c r="J45">
-        <f t="shared" si="12"/>
+        <f>COUNT(J5,J6,J7,J8,J9,J10,J11,J12,J13,J15,J16,J17,J18,J20,J22,J24,J25,J26,J27,J28,J29,J30,J31,J33,J34,J35,J37,J39)</f>
         <v>0</v>
       </c>
       <c r="K45">
-        <f t="shared" si="12"/>
+        <f>COUNT(K5,K6,K7,K8,K9,K10,K11,K12,K13,K15,K16,K17,K18,K20,K22,K24,K25,K26,K27,K28,K29,K30,K31,K33,K34,K35,K37,K39)</f>
         <v>0</v>
       </c>
       <c r="L45">
-        <f t="shared" si="12"/>
+        <f>COUNT(L5,L6,L7,L8,L9,L10,L11,L12,L13,L15,L16,L17,L18,L20,L22,L24,L25,L26,L27,L28,L29,L30,L31,L33,L34,L35,L37,L39)</f>
         <v>0</v>
       </c>
       <c r="M45">
-        <f t="shared" si="12"/>
+        <f>COUNT(M5,M6,M7,M8,M9,M10,M11,M12,M13,M15,M16,M17,M18,M20,M22,M24,M25,M26,M27,M28,M29,M30,M31,M33,M34,M35,M37,M39)</f>
         <v>0</v>
       </c>
       <c r="N45">
-        <f t="shared" si="12"/>
+        <f>COUNT(N5,N6,N7,N8,N9,N10,N11,N12,N13,N15,N16,N17,N18,N20,N22,N24,N25,N26,N27,N28,N29,N30,N31,N33,N34,N35,N37,N39)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A24:A31"/>
     <mergeCell ref="A33:A35"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A24:A31"/>
   </mergeCells>
-  <phoneticPr fontId="12"/>
   <conditionalFormatting sqref="D42:N44">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C39:N39 C37:N37 C33:N35 C5:N13 C22:N22 C20:N20 C15:N18 C24:N31" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="28">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C5:N5">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C6:N6">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C7:N7">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C8:N8">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C9:N9">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C10:N10">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C11:N11">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C12:N12">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C13:N13">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C15:N15">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C16:N16">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C17:N17">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C18:N18">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C20:N20">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C22:N22">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C24:N24">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C25:N25">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C26:N26">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C27:N27">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C28:N28">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C29:N29">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C30:N30">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C31:N31">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C33:N33">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C34:N34">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C35:N35">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C37:N37">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力を確認してください" error="0以上の半角数字で入力してください。" promptTitle="月末残高" prompt="円換算した0以上の整数を入力してください。" sqref="C39:N39">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -3696,191 +3784,187 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FFC9A84C"/>
   </sheetPr>
-  <dimension ref="B1:M52"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.75" customWidth="1"/>
-    <col min="2" max="13" width="13.75" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="13" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="2:13" ht="34" customHeight="1">
+      <c r="B1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-    </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B2" s="15" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="2:13">
+      <c r="B2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B4" s="22" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22" t="s">
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B5" s="23" t="str">
-        <f>IFERROR(LOOKUP(2,1/(資産記録!$C$45:$N$45&gt;0),資産記録!$C$4:$N$4),"未入力")</f>
-        <v>2026年3月</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="24">
-        <f>IFERROR(LOOKUP(2,1/(資産記録!$C$45:$N$45&gt;0),資産記録!$C$41:$N$41),0)</f>
-        <v>1357000</v>
-      </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24">
-        <f>IFERROR(LOOKUP(2,1/(資産記録!$C$45:$N$45&gt;0),資産記録!$C$42:$N$42),0)</f>
-        <v>104800</v>
-      </c>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B8" s="22" t="s">
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="22" t="str">
+        <f>IFERROR(LOOKUP(2,1/('資産記録'!$C$45:$N$45&gt;0),'資産記録'!$C$4:$N$4),"未入力")</f>
+        <v>未入力</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="23">
+        <f>IFERROR(LOOKUP(2,1/('資産記録'!$C$45:$N$45&gt;0),'資産記録'!$C$41:$N$41),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23" t="str">
+        <f>IFERROR(LOOKUP(2,1/('資産記録'!$C$45:$N$45&gt;0),IF(ISNUMBER('資産記録'!$C$42:$N$42),'資産記録'!$C$42:$N$42,"比較不可")),"未入力")</f>
+        <v>未入力</v>
+      </c>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="15" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B9" s="24">
-        <f>IFERROR(LOOKUP(2,1/(資産記録!$C$45:$N$45&gt;0),資産記録!$C$44:$N$44),0)</f>
-        <v>255000</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B51" s="15" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="23" t="str">
+        <f>IFERROR(LOOKUP(2,1/('資産記録'!$C$45:$N$45&gt;0),IF(ISNUMBER('資産記録'!$C$44:$N$44),'資産記録'!$C$44:$N$44,"比較不可")),"未入力")</f>
+        <v>未入力</v>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="51" spans="2:13">
+      <c r="B51" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
-    </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" spans="2:13">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E10"/>
-    <mergeCell ref="F8:M10"/>
-    <mergeCell ref="B51:M52"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B4:E4"/>
@@ -3889,305 +3973,475 @@
     <mergeCell ref="F5:I6"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="J5:M6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E10"/>
+    <mergeCell ref="F8:M10"/>
+    <mergeCell ref="B51:M52"/>
   </mergeCells>
-  <phoneticPr fontId="12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF132238"/>
   </sheetPr>
-  <dimension ref="B1:H33"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.75" customWidth="1"/>
-    <col min="2" max="2" width="22.75" customWidth="1"/>
-    <col min="3" max="8" width="15.75" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="8" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="2:8" ht="34" customHeight="1">
+      <c r="B1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B2" s="15" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="2:8">
+      <c r="B2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="4" spans="2:8" ht="15" x14ac:dyDescent="0.15">
-      <c r="B4" s="25" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B5" s="26" t="s">
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-    </row>
-    <row r="10" spans="2:8" ht="15" x14ac:dyDescent="0.15">
-      <c r="B10" s="25" t="s">
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B11" s="26" t="s">
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-    </row>
-    <row r="16" spans="2:8" ht="15" x14ac:dyDescent="0.15">
-      <c r="B16" s="25" t="s">
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B17" s="26" t="s">
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-    </row>
-    <row r="22" spans="2:8" ht="15" x14ac:dyDescent="0.15">
-      <c r="B22" s="25" t="s">
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B23" s="26" t="s">
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B28" s="27" t="s">
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-    </row>
-    <row r="33" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="s">
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="27" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B28:H31"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H8"/>
+    <mergeCell ref="B10:H10"/>
     <mergeCell ref="B11:H14"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B17:H20"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B23:H26"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H8"/>
-    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B28:H31"/>
   </mergeCells>
-  <phoneticPr fontId="12"/>
   <hyperlinks>
-    <hyperlink ref="B33" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="B33" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="34" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="6">
+        <v>300000</v>
+      </c>
+      <c r="C6" s="6">
+        <v>250000</v>
+      </c>
+      <c r="D6" s="6">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="6">
+        <v>100000</v>
+      </c>
+      <c r="C7" s="6">
+        <v>120000</v>
+      </c>
+      <c r="D7" s="6">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1080000</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="6">
+        <v>500000</v>
+      </c>
+      <c r="C9" s="6">
+        <v>520000</v>
+      </c>
+      <c r="D9" s="6">
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="17">
+        <f>SUM(B6:B9)</f>
+        <v>1900000</v>
+      </c>
+      <c r="C10" s="17">
+        <f>SUM(C6:C9)</f>
+        <v>1970000</v>
+      </c>
+      <c r="D10" s="17">
+        <f>SUM(D6:D9)</f>
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="19">
+        <f>C10-B10</f>
+        <v>70000</v>
+      </c>
+      <c r="D11" s="19">
+        <f>D10-C10</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="A13:D16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>